--- a/sampleprojects/TaxReturn/excel/states/SC.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/SC.xlsx
@@ -134,13 +134,13 @@
     <t>Apply joint standard deduction</t>
   </si>
   <si>
-    <t>set result.sc_taxable_income = the maximum of (result.agi - sc_standard_deduction_joint) and 0</t>
+    <t>set result.sc_taxable_income = the maximum of (result.state_calc_agi - sc_standard_deduction_joint) and 0</t>
   </si>
   <si>
     <t>Apply single standard deduction</t>
   </si>
   <si>
-    <t>set result.sc_taxable_income = the maximum of (result.agi - sc_standard_deduction_single) and 0</t>
+    <t>set result.sc_taxable_income = the maximum of (result.state_calc_agi - sc_standard_deduction_single) and 0</t>
   </si>
   <si>
     <t>DT: SC Tax Brackets</t>
